--- a/public/exports-from-60-with-coowners/29189811.xlsx
+++ b/public/exports-from-60-with-coowners/29189811.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -17839,12 +17839,12 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896977</t>
+          <t xml:space="preserve">311896978</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M238" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189811.xlsx
+++ b/public/exports-from-60-with-coowners/29189811.xlsx
@@ -1031,11 +1031,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J14">
-        <v>341</v>
+        <v>227</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Kanalvej 1C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290907</t>
+          <t xml:space="preserve">5076111</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J15">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,17 +1166,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kanalvej 1C</t>
+          <t xml:space="preserve">Kirkegade 5A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5076111</t>
+          <t xml:space="preserve">5107615</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="J16">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 5A</t>
+          <t xml:space="preserve">Kongsgaardsvej 24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,16 +1251,16 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107615</t>
+          <t xml:space="preserve">736955, 5759230</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J17">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsgaardsvej 24</t>
+          <t xml:space="preserve">Laboratorievej 14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">736955, 5759230</t>
+          <t xml:space="preserve">736990, 5755769</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laboratorievej 14</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,16 +1401,16 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">736990, 5755769</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J19">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1466,26 +1466,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">9212294</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J20">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J21">
@@ -1631,11 +1631,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J22">
-        <v>254</v>
+        <v>812</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1691,26 +1691,26 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Skadehøjvej 2A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212294</t>
+          <t xml:space="preserve">736999, 5757026</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J23">
-        <v>812</v>
+        <v>206</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,26 +1766,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skadehøjvej 2A</t>
+          <t xml:space="preserve">Skolegade 22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">736999, 5757026</t>
+          <t xml:space="preserve">5081117</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J24">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,26 +1841,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 22</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081117</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J25">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Strandvejen 415A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6854</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5091706</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J26">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,26 +1991,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 415A</t>
+          <t xml:space="preserve">Strandvejen 9A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6854</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5091706</t>
+          <t xml:space="preserve">8939771</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J27">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,26 +2066,26 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 9A</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939771</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J28">
-        <v>104</v>
+        <v>508</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Vestergade 5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">5081928</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2226,16 +2226,16 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081928</t>
+          <t xml:space="preserve">5081936</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>503</v>
+        <v>267</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081936</t>
+          <t xml:space="preserve">5081974</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J31">
-        <v>267</v>
+        <v>2228</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 5</t>
+          <t xml:space="preserve">Vestergade 7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,16 +2376,16 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081974</t>
+          <t xml:space="preserve">7559492</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J32">
-        <v>2228</v>
+        <v>117</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 7</t>
+          <t xml:space="preserve">Vestergade 9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,11 +2456,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J33">
-        <v>117</v>
+        <v>215</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 9</t>
+          <t xml:space="preserve">Vænget 51</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7559492</t>
+          <t xml:space="preserve">7564727</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J34">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vænget 51</t>
+          <t xml:space="preserve">Æblevej 7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6852</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">7564727</t>
+          <t xml:space="preserve">5089553, 100197175</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="J35">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Æblevej 7</t>
+          <t xml:space="preserve">Østparken 129B</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6852</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089553, 100197175</t>
+          <t xml:space="preserve">5088609</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,17 +2741,17 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østparken 129B</t>
+          <t xml:space="preserve">Vesterled 50A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088609</t>
+          <t xml:space="preserve">5094591</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,26 +2760,26 @@
         </is>
       </c>
       <c r="J37">
-        <v>160</v>
+        <v>1136</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve">200044645</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-01-21</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -2816,30 +2816,30 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 50A</t>
+          <t xml:space="preserve">Højgårdsparken 1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094591</t>
+          <t xml:space="preserve">1511503</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J38">
-        <v>1136</v>
+        <v>257</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">200044645</t>
+          <t xml:space="preserve">200048960</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-01-21</t>
+          <t xml:space="preserve">2021-05-10</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Kommune</t>
+          <t xml:space="preserve">HELLE HALLEN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsparken 1</t>
+          <t xml:space="preserve">Hellevej 27B</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511503</t>
+          <t xml:space="preserve">737253, 5113535</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J39">
-        <v>257</v>
+        <v>96</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">200048960</t>
+          <t xml:space="preserve">310033483</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-10</t>
+          <t xml:space="preserve">2023-04-05</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HELLE HALLEN</t>
+          <t xml:space="preserve">Varde Kommune</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2966,50 +2966,50 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hellevej 27B</t>
+          <t xml:space="preserve">Tirpitzvej 1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">737253, 5113535</t>
+          <t xml:space="preserve">7867969</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J40">
-        <v>96</v>
+        <v>2870</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">310033483</t>
+          <t xml:space="preserve">311253609</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">FULDENDT P/S</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-05</t>
+          <t xml:space="preserve">2027-06-13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -3041,40 +3041,40 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tirpitzvej 1</t>
+          <t xml:space="preserve">Rosenvænget 45</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7867969</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J41">
-        <v>2870</v>
+        <v>1565</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253609</t>
+          <t xml:space="preserve">311490959</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FULDENDT P/S</t>
+          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-13</t>
+          <t xml:space="preserve">2031-01-27</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,40 +3116,40 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 45</t>
+          <t xml:space="preserve">Ortenvej 64</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">1511445</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J42">
-        <v>1565</v>
+        <v>9958</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311490959</t>
+          <t xml:space="preserve">311523520</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEEN MILJØ &amp; ENERGIRÅDGIVNING ApS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-27</t>
+          <t xml:space="preserve">2031-05-28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,40 +3191,40 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ortenvej 64</t>
+          <t xml:space="preserve">Skovparken 5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511445</t>
+          <t xml:space="preserve">100177775</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>9958</v>
+        <v>3020</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311523520</t>
+          <t xml:space="preserve">311547428</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-28</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Kommune</t>
+          <t xml:space="preserve">Varde Bolig Administration</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3266,40 +3266,40 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovparken 5</t>
+          <t xml:space="preserve">Hornelund 27A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">100177775</t>
+          <t xml:space="preserve">316354, 316355</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>3020</v>
+        <v>1312</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547428</t>
+          <t xml:space="preserve">311640988</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2032-11-07</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornelund 27A</t>
+          <t xml:space="preserve">Frisvadvej 1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,20 +3351,20 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">316354, 316355</t>
+          <t xml:space="preserve">319575, 319576</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J45">
-        <v>1312</v>
+        <v>4192</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311640988</t>
+          <t xml:space="preserve">311643012</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-07</t>
+          <t xml:space="preserve">2032-11-16</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frisvadvej 1</t>
+          <t xml:space="preserve">Bredgade 50A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3426,20 +3426,20 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">319575, 319576</t>
+          <t xml:space="preserve">315395, 315396</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>4192</v>
+        <v>1585</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643012</t>
+          <t xml:space="preserve">311648415</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-16</t>
+          <t xml:space="preserve">2032-12-11</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Bolig Administration</t>
+          <t xml:space="preserve">Varde Kommune</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3491,17 +3491,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 50A</t>
+          <t xml:space="preserve">Lærkevej 8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">315395, 315396</t>
+          <t xml:space="preserve">5080884</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="J47">
-        <v>1585</v>
+        <v>5683</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648415</t>
+          <t xml:space="preserve">311686380</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-11</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lærkevej 8</t>
+          <t xml:space="preserve">Lyngparken 1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5080884</t>
+          <t xml:space="preserve">319097, 319098</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,21 +3585,21 @@
         </is>
       </c>
       <c r="J48">
-        <v>5683</v>
+        <v>3711</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686380</t>
+          <t xml:space="preserve">311711209</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2033-09-28</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Kommune</t>
+          <t xml:space="preserve">Boligselskabet Filsø</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 1</t>
+          <t xml:space="preserve">Kirkegade 71</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">319097, 319098</t>
+          <t xml:space="preserve">315411, 315412</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>3711</v>
+        <v>470</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311711209</t>
+          <t xml:space="preserve">311713168</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-28</t>
+          <t xml:space="preserve">2033-10-06</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Filsø</t>
+          <t xml:space="preserve">Bolig Syd Vest</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 71</t>
+          <t xml:space="preserve">Humlehaven 59</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">315411, 315412</t>
+          <t xml:space="preserve">319095, 319096</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>470</v>
+        <v>432</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311713168</t>
+          <t xml:space="preserve">311715799</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-06</t>
+          <t xml:space="preserve">2033-10-17</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Humlehaven 59</t>
+          <t xml:space="preserve">Kærhøgevej 4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">319095, 319096</t>
+          <t xml:space="preserve">319138, 319139</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715799</t>
+          <t xml:space="preserve">311715798</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolig Syd Vest</t>
+          <t xml:space="preserve">Varde Kommune</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøgevej 4</t>
+          <t xml:space="preserve">Møllegårdsvej 9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">319138, 319139</t>
+          <t xml:space="preserve">5079556</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J52">
-        <v>423</v>
+        <v>917</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311715798</t>
+          <t xml:space="preserve">311730890</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-17</t>
+          <t xml:space="preserve">2033-12-21</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Kommune</t>
+          <t xml:space="preserve">ARBEJDERNES ANDELS-BOLIGFORENING</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3941,40 +3941,40 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegårdsvej 9</t>
+          <t xml:space="preserve">Lyngparken 1A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079556</t>
+          <t xml:space="preserve">7991607, 100833352</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J53">
-        <v>917</v>
+        <v>77</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730890</t>
+          <t xml:space="preserve">311775359</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-21</t>
+          <t xml:space="preserve">2034-07-29</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARBEJDERNES ANDELS-BOLIGFORENING</t>
+          <t xml:space="preserve">Varde Kommune</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 1A</t>
+          <t xml:space="preserve">Egekrattet 7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,30 +4026,30 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">7991607, 100833352</t>
+          <t xml:space="preserve">100545090</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>77</v>
+        <v>989</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775359</t>
+          <t xml:space="preserve">311777304</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-29</t>
+          <t xml:space="preserve">2034-08-09</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 7</t>
+          <t xml:space="preserve">Vesterbækvej 31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,30 +4101,30 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">100545090</t>
+          <t xml:space="preserve">7427707</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J55">
-        <v>989</v>
+        <v>2030</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311777304</t>
+          <t xml:space="preserve">311832916</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-09</t>
+          <t xml:space="preserve">2035-05-20</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterbækvej 31</t>
+          <t xml:space="preserve">Bredgade 55</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4176,30 +4176,30 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">7427707</t>
+          <t xml:space="preserve">5107640</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J56">
-        <v>2030</v>
+        <v>718</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832916</t>
+          <t xml:space="preserve">311844281</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-20</t>
+          <t xml:space="preserve">2035-07-11</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 55</t>
+          <t xml:space="preserve">Lerpøtvej 50A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107640</t>
+          <t xml:space="preserve">5755831</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="J57">
-        <v>718</v>
+        <v>521</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844281</t>
+          <t xml:space="preserve">311844284</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50A</t>
+          <t xml:space="preserve">Lerpøtvej 50B</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J58">
-        <v>521</v>
+        <v>674</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50B</t>
+          <t xml:space="preserve">Lerpøtvej 50C</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J59">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4466,30 +4466,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 50C</t>
+          <t xml:space="preserve">Storegade 59</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755831</t>
+          <t xml:space="preserve">7968232</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>709</v>
+        <v>612</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844284</t>
+          <t xml:space="preserve">311844285</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J61">
-        <v>612</v>
+        <v>1830</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4631,11 +4631,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J62">
-        <v>1830</v>
+        <v>233</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4706,11 +4706,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J63">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4781,11 +4781,11 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J64">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,40 +4841,40 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 59</t>
+          <t xml:space="preserve">Sønderalle 7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968232</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J65">
-        <v>210</v>
+        <v>449</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311844285</t>
+          <t xml:space="preserve">311863487</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-07-11</t>
+          <t xml:space="preserve">2035-10-22</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderalle 7</t>
+          <t xml:space="preserve">Krovej 11B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">8296451</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,21 +4935,21 @@
         </is>
       </c>
       <c r="J66">
-        <v>449</v>
+        <v>635</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311863487</t>
+          <t xml:space="preserve">311869486</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-22</t>
+          <t xml:space="preserve">2035-11-20</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krovej 11B</t>
+          <t xml:space="preserve">Troesmosevej 2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8296451</t>
+          <t xml:space="preserve">9998735</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,11 +5010,11 @@
         </is>
       </c>
       <c r="J67">
-        <v>635</v>
+        <v>1403</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869486</t>
+          <t xml:space="preserve">311869806</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-20</t>
+          <t xml:space="preserve">2035-11-24</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>1403</v>
+        <v>3244</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5156,11 +5156,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J69">
-        <v>3244</v>
+        <v>634</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5231,15 +5231,15 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J70">
-        <v>634</v>
+        <v>973</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869806</t>
+          <t xml:space="preserve">311869804</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Troesmosevej 2</t>
+          <t xml:space="preserve">Byagervej 10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">9998735</t>
+          <t xml:space="preserve">5099694</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>973</v>
+        <v>126</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869804</t>
+          <t xml:space="preserve">311876600</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-24</t>
+          <t xml:space="preserve">2036-01-14</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 10</t>
+          <t xml:space="preserve">Byagervej 14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J72">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 14</t>
+          <t xml:space="preserve">Byagervej 18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J73">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 18</t>
+          <t xml:space="preserve">Fredensvej 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099694</t>
+          <t xml:space="preserve">5088173</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J74">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876600</t>
+          <t xml:space="preserve">311876611</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 1</t>
+          <t xml:space="preserve">Fredensvej 11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J75">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 11</t>
+          <t xml:space="preserve">Fredensvej 12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5681,11 +5681,11 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J76">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 12</t>
+          <t xml:space="preserve">Fredensvej 13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J77">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 13</t>
+          <t xml:space="preserve">Fredensvej 16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J78">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 16</t>
+          <t xml:space="preserve">Fredensvej 3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J79">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 3</t>
+          <t xml:space="preserve">Fredensvej 4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J80">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 4</t>
+          <t xml:space="preserve">Fredensvej 5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J81">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 5</t>
+          <t xml:space="preserve">Fredensvej 6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J82">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 6</t>
+          <t xml:space="preserve">Fredensvej 7</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J83">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 7</t>
+          <t xml:space="preserve">Fredensvej 9</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J84">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredensvej 9</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088173</t>
+          <t xml:space="preserve">5081870</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J85">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876611</t>
+          <t xml:space="preserve">311876602</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Nørregade 7B</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7B</t>
+          <t xml:space="preserve">Nørregade 7D</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7D</t>
+          <t xml:space="preserve">Nørregade 7E</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7E</t>
+          <t xml:space="preserve">Nørregade 7F</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J89">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7F</t>
+          <t xml:space="preserve">Nørregade 7G</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J90">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7G</t>
+          <t xml:space="preserve">Nørregade 7H</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J91">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7H</t>
+          <t xml:space="preserve">Nørregade 7K</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J92">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7K</t>
+          <t xml:space="preserve">Nørregade 7L</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J93">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7L</t>
+          <t xml:space="preserve">Nørregade 7M</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J94">
@@ -7091,30 +7091,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7M</t>
+          <t xml:space="preserve">Blüchers Alle 9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081870</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J95">
-        <v>60</v>
+        <v>494</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876602</t>
+          <t xml:space="preserve">311876778</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-14</t>
+          <t xml:space="preserve">2036-01-15</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blüchers Alle 9</t>
+          <t xml:space="preserve">Fåborgvej 88A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112164</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>494</v>
+        <v>237</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876778</t>
+          <t xml:space="preserve">311876777</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 88A</t>
+          <t xml:space="preserve">Fåborgvej 90</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,15 +7256,15 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J97">
-        <v>237</v>
+        <v>408</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876777</t>
+          <t xml:space="preserve">311876768</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 90</t>
+          <t xml:space="preserve">Skolegade 15</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112164</t>
+          <t xml:space="preserve">5081153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>408</v>
+        <v>250</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876768</t>
+          <t xml:space="preserve">311876774</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 15</t>
+          <t xml:space="preserve">Skolegade 24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,20 +7401,20 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081153</t>
+          <t xml:space="preserve">5081116</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>250</v>
+        <v>351</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876774</t>
+          <t xml:space="preserve">311876773</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 24</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081116</t>
+          <t xml:space="preserve">5081191</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>351</v>
+        <v>2264</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876773</t>
+          <t xml:space="preserve">311876775</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,17 +7541,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Sønderskovvej 107</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081191</t>
+          <t xml:space="preserve">5135329</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,11 +7560,11 @@
         </is>
       </c>
       <c r="J101">
-        <v>2264</v>
+        <v>4847</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876775</t>
+          <t xml:space="preserve">311876769</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 107</t>
+          <t xml:space="preserve">Debelvej 23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5135329</t>
+          <t xml:space="preserve">5112771</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>4847</v>
+        <v>5820</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876769</t>
+          <t xml:space="preserve">311878341</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-15</t>
+          <t xml:space="preserve">2036-01-23</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J103">
-        <v>5820</v>
+        <v>1100</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 23</t>
+          <t xml:space="preserve">Debelvej 25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112771</t>
+          <t xml:space="preserve">100043834</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>1100</v>
+        <v>620</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878341</t>
+          <t xml:space="preserve">311878336</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,30 +7841,30 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debelvej 25</t>
+          <t xml:space="preserve">Højgårdsparken 69</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">100043834</t>
+          <t xml:space="preserve">100064656</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>620</v>
+        <v>108</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878336</t>
+          <t xml:space="preserve">311878339</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højgårdsparken 69</t>
+          <t xml:space="preserve">Stationsvej 2A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064656</t>
+          <t xml:space="preserve">5075657</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878339</t>
+          <t xml:space="preserve">311878457</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-23</t>
+          <t xml:space="preserve">2036-01-24</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2A</t>
+          <t xml:space="preserve">Stationsvej 2B</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J107">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2B</t>
+          <t xml:space="preserve">Stationsvej 2C</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J108">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2C</t>
+          <t xml:space="preserve">Stationsvej 2D</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075657</t>
+          <t xml:space="preserve">5075762</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878457</t>
+          <t xml:space="preserve">311878458</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2D</t>
+          <t xml:space="preserve">Stationsvej 2E</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J110">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 2E</t>
+          <t xml:space="preserve">Søndergade 76</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075762</t>
+          <t xml:space="preserve">5082503</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>60</v>
+        <v>264</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878458</t>
+          <t xml:space="preserve">311878455</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J112">
-        <v>264</v>
+        <v>198</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J113">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 76</t>
+          <t xml:space="preserve">Falkevej 4A</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082503</t>
+          <t xml:space="preserve">317690, 317691</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>198</v>
+        <v>1070</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878455</t>
+          <t xml:space="preserve">311878488</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-24</t>
+          <t xml:space="preserve">2036-01-25</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falkevej 4A</t>
+          <t xml:space="preserve">Højvangen 4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">317690, 317691</t>
+          <t xml:space="preserve">5078282</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>1070</v>
+        <v>457</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878488</t>
+          <t xml:space="preserve">311878485</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangen 4</t>
+          <t xml:space="preserve">Mælkevejen 1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,20 +8676,20 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078282</t>
+          <t xml:space="preserve">5078139</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J116">
-        <v>457</v>
+        <v>209</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878485</t>
+          <t xml:space="preserve">311878489</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8756,15 +8756,15 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>209</v>
+        <v>1440</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878489</t>
+          <t xml:space="preserve">311878543</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-25</t>
+          <t xml:space="preserve">2036-01-26</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J118">
-        <v>1440</v>
+        <v>554</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,30 +8891,30 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mælkevejen 1</t>
+          <t xml:space="preserve">Møllevej 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078139</t>
+          <t xml:space="preserve">5113229</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>554</v>
+        <v>380</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878543</t>
+          <t xml:space="preserve">311878765</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-26</t>
+          <t xml:space="preserve">2036-01-27</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 1</t>
+          <t xml:space="preserve">Egekrattet 10</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5113229</t>
+          <t xml:space="preserve">8165975</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311878765</t>
+          <t xml:space="preserve">311881488</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-27</t>
+          <t xml:space="preserve">2036-02-11</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 10</t>
+          <t xml:space="preserve">Egekrattet 8</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165975</t>
+          <t xml:space="preserve">8165976</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,11 +9060,11 @@
         </is>
       </c>
       <c r="J121">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881488</t>
+          <t xml:space="preserve">311881489</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egekrattet 8</t>
+          <t xml:space="preserve">Kærhøgevej 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165976</t>
+          <t xml:space="preserve">1809437</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>370</v>
+        <v>497</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881489</t>
+          <t xml:space="preserve">311881487</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9191,17 +9191,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærhøgevej 2</t>
+          <t xml:space="preserve">Skolegade 22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809437</t>
+          <t xml:space="preserve">5081117</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>497</v>
+        <v>1693</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881487</t>
+          <t xml:space="preserve">311881490</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 22</t>
+          <t xml:space="preserve">Stationsvej 19</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081117</t>
+          <t xml:space="preserve">5079228</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,11 +9285,11 @@
         </is>
       </c>
       <c r="J124">
-        <v>1693</v>
+        <v>528</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881490</t>
+          <t xml:space="preserve">311881512</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 19</t>
+          <t xml:space="preserve">Thorstrupvej 14</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079228</t>
+          <t xml:space="preserve">5078819</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -9360,11 +9360,11 @@
         </is>
       </c>
       <c r="J125">
-        <v>528</v>
+        <v>381</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881512</t>
+          <t xml:space="preserve">311881515</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 14</t>
+          <t xml:space="preserve">Thorstrupvej 16</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9431,15 +9431,15 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881515</t>
+          <t xml:space="preserve">311881519</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 16</t>
+          <t xml:space="preserve">Thorstrupvej 18</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078819</t>
+          <t xml:space="preserve">5078814</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>296</v>
+        <v>3019</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881519</t>
+          <t xml:space="preserve">311881536</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thorstrupvej 18</t>
+          <t xml:space="preserve">Grødevej 7</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5078814</t>
+          <t xml:space="preserve">5076159</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>3019</v>
+        <v>423</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881536</t>
+          <t xml:space="preserve">311881912</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-11</t>
+          <t xml:space="preserve">2036-02-13</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grødevej 7</t>
+          <t xml:space="preserve">Stilbjergvej 30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5076159</t>
+          <t xml:space="preserve">5759719</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J129">
-        <v>423</v>
+        <v>151</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881912</t>
+          <t xml:space="preserve">311882129</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-13</t>
+          <t xml:space="preserve">2036-02-16</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stilbjergvej 30</t>
+          <t xml:space="preserve">Bredgade 39</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,20 +9726,20 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5759719</t>
+          <t xml:space="preserve">5107083</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>151</v>
+        <v>3381</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311882129</t>
+          <t xml:space="preserve">311883233</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-16</t>
+          <t xml:space="preserve">2036-02-20</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 39</t>
+          <t xml:space="preserve">Gartnerpassagen 6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107083</t>
+          <t xml:space="preserve">5082163</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>3381</v>
+        <v>4305</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883233</t>
+          <t xml:space="preserve">311883263</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gartnerpassagen 6</t>
+          <t xml:space="preserve">Jægumsvej 44</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5082163</t>
+          <t xml:space="preserve">5758115</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,11 +9885,11 @@
         </is>
       </c>
       <c r="J132">
-        <v>4305</v>
+        <v>643</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883263</t>
+          <t xml:space="preserve">311883267</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jægumsvej 44</t>
+          <t xml:space="preserve">Kildegårdvej 14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6852</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5758115</t>
+          <t xml:space="preserve">5089317</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>643</v>
+        <v>1744</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883267</t>
+          <t xml:space="preserve">311883204</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegårdvej 14</t>
+          <t xml:space="preserve">Kløvbakken 70</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">6852</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089317</t>
+          <t xml:space="preserve">8245265</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>1744</v>
+        <v>452</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883204</t>
+          <t xml:space="preserve">311883265</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J135">
-        <v>452</v>
+        <v>68</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvbakken 70</t>
+          <t xml:space="preserve">Krogen 1</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8245265</t>
+          <t xml:space="preserve">5755579</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>68</v>
+        <v>366</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883265</t>
+          <t xml:space="preserve">311883234</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 1</t>
+          <t xml:space="preserve">Pramstedvej 10C</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755579</t>
+          <t xml:space="preserve">5755568</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>366</v>
+        <v>8223</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883234</t>
+          <t xml:space="preserve">311883211</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 10C</t>
+          <t xml:space="preserve">Pramstedvej 12B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755568</t>
+          <t xml:space="preserve">5759376</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J138">
-        <v>8223</v>
+        <v>504</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883211</t>
+          <t xml:space="preserve">311883210</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12B</t>
+          <t xml:space="preserve">Pramstedvej 12C</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,15 +10406,15 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J139">
-        <v>504</v>
+        <v>171</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883210</t>
+          <t xml:space="preserve">311883208</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12C</t>
+          <t xml:space="preserve">Pramstedvej 12D</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883208</t>
+          <t xml:space="preserve">311883209</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 12D</t>
+          <t xml:space="preserve">Storegade 57</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5759376</t>
+          <t xml:space="preserve">5754327</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>171</v>
+        <v>1377</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883209</t>
+          <t xml:space="preserve">311883205</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 57</t>
+          <t xml:space="preserve">Torvet 9</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754327</t>
+          <t xml:space="preserve">7925073</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>1377</v>
+        <v>234</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883205</t>
+          <t xml:space="preserve">311883262</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 9</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">7925073</t>
+          <t xml:space="preserve">5088167</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>234</v>
+        <v>3489</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883262</t>
+          <t xml:space="preserve">311883264</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Østervang 1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088167</t>
+          <t xml:space="preserve">5757498</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>3489</v>
+        <v>502</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883264</t>
+          <t xml:space="preserve">311883232</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 1</t>
+          <t xml:space="preserve">Bredgade 35</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,20 +10851,20 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757498</t>
+          <t xml:space="preserve">5107083</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J145">
-        <v>502</v>
+        <v>123</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883232</t>
+          <t xml:space="preserve">311883506</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-20</t>
+          <t xml:space="preserve">2036-02-23</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 35</t>
+          <t xml:space="preserve">Bredgade 37</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J146">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 37</t>
+          <t xml:space="preserve">Dalgasvej 35</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,20 +11001,20 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107083</t>
+          <t xml:space="preserve">5754804</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>244</v>
+        <v>413</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311883506</t>
+          <t xml:space="preserve">311888577</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-23</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11081,11 +11081,11 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J148">
-        <v>413</v>
+        <v>374</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgasvej 35</t>
+          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,20 +11151,20 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5754804</t>
+          <t xml:space="preserve">10002269</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J149">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888577</t>
+          <t xml:space="preserve">311888784</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbjerg Møllevej 69A</t>
+          <t xml:space="preserve">Isbjerg Møllevej 69B</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11231,15 +11231,15 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888784</t>
+          <t xml:space="preserve">311888782</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isbjerg Møllevej 69B</t>
+          <t xml:space="preserve">Rosenvænget 31</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">10002269</t>
+          <t xml:space="preserve">7767753</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>148</v>
+        <v>335</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888782</t>
+          <t xml:space="preserve">311888779</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>335</v>
+        <v>490</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J153">
-        <v>490</v>
+        <v>157</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J154">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11606,15 +11606,15 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J155">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888779</t>
+          <t xml:space="preserve">311888781</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 31</t>
+          <t xml:space="preserve">Skolegade 25</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7767753</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J156">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888781</t>
+          <t xml:space="preserve">311888764</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 25</t>
+          <t xml:space="preserve">Skolegade 27F</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">100083815</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>419</v>
+        <v>985</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888764</t>
+          <t xml:space="preserve">311888580</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27F</t>
+          <t xml:space="preserve">Svanehøjvej 27</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">100083815</t>
+          <t xml:space="preserve">9212270</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,11 +11835,11 @@
         </is>
       </c>
       <c r="J158">
-        <v>985</v>
+        <v>2216</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888580</t>
+          <t xml:space="preserve">311888785</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Svanehøjvej 27</t>
+          <t xml:space="preserve">Toften 2H</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212270</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J159">
-        <v>2216</v>
+        <v>512</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888785</t>
+          <t xml:space="preserve">311888770</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,30 +11966,30 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toften 2H</t>
+          <t xml:space="preserve">Vadgårdsvej 17</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5099212</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J160">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888770</t>
+          <t xml:space="preserve">311888780</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,17 +12041,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vadgårdsvej 17</t>
+          <t xml:space="preserve">Vardevej 1A</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099212</t>
+          <t xml:space="preserve">5106531</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,11 +12060,11 @@
         </is>
       </c>
       <c r="J161">
-        <v>525</v>
+        <v>2544</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888780</t>
+          <t xml:space="preserve">311888776</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1A</t>
+          <t xml:space="preserve">Vardevej 1B</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>2544</v>
+        <v>428</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888776</t>
+          <t xml:space="preserve">311888760</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,30 +12191,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vardevej 1B</t>
+          <t xml:space="preserve">Vestervold 11A</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106531</t>
+          <t xml:space="preserve">5756377</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>428</v>
+        <v>1527</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888760</t>
+          <t xml:space="preserve">311888579</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11A</t>
+          <t xml:space="preserve">Vestervold 11C</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756377</t>
+          <t xml:space="preserve">5756447</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1527</v>
+        <v>384</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888579</t>
+          <t xml:space="preserve">311888578</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11C</t>
+          <t xml:space="preserve">Vestervold 11D</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756447</t>
+          <t xml:space="preserve">5756377</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J165">
-        <v>384</v>
+        <v>154</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888578</t>
+          <t xml:space="preserve">311888579</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervold 11D</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756377</t>
+          <t xml:space="preserve">1511385</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>154</v>
+        <v>3442</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888579</t>
+          <t xml:space="preserve">311888935</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-03-20</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>3442</v>
+        <v>969</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12581,11 +12581,11 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J168">
-        <v>969</v>
+        <v>1067</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12656,11 +12656,11 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J169">
-        <v>1067</v>
+        <v>1052</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Abildvej 35</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12731,15 +12731,15 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J170">
-        <v>1052</v>
+        <v>1970</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888935</t>
+          <t xml:space="preserve">311888912</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 35</t>
+          <t xml:space="preserve">Kirkegade 3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511385</t>
+          <t xml:space="preserve">8367028</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>1970</v>
+        <v>147</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888912</t>
+          <t xml:space="preserve">311888953</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12866,17 +12866,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 3</t>
+          <t xml:space="preserve">Lindealle 8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8367028</t>
+          <t xml:space="preserve">5081802</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,11 +12885,11 @@
         </is>
       </c>
       <c r="J172">
-        <v>147</v>
+        <v>778</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888953</t>
+          <t xml:space="preserve">311888957</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindealle 8</t>
+          <t xml:space="preserve">Skolegade 11</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,20 +12951,20 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081802</t>
+          <t xml:space="preserve">5081139</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J173">
-        <v>778</v>
+        <v>1624</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888957</t>
+          <t xml:space="preserve">311888955</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J174">
-        <v>1624</v>
+        <v>2910</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13106,11 +13106,11 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J175">
-        <v>2910</v>
+        <v>740</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13181,11 +13181,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J176">
-        <v>740</v>
+        <v>460</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13256,11 +13256,11 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J177">
-        <v>460</v>
+        <v>241</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 11</t>
+          <t xml:space="preserve">Bytoften 2</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5081139</t>
+          <t xml:space="preserve">5756643</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J178">
-        <v>241</v>
+        <v>6003</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888955</t>
+          <t xml:space="preserve">311892635</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-20</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 2</t>
+          <t xml:space="preserve">Flyvepladsvej 2B</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756643</t>
+          <t xml:space="preserve">5107795</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J179">
-        <v>6003</v>
+        <v>265</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892635</t>
+          <t xml:space="preserve">311892714</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flyvepladsvej 2B</t>
+          <t xml:space="preserve">Kirkegade 1B</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,20 +13476,20 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107795</t>
+          <t xml:space="preserve">5107190</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J180">
-        <v>265</v>
+        <v>1435</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892714</t>
+          <t xml:space="preserve">311892637</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,30 +13541,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1B</t>
+          <t xml:space="preserve">Kirkegade 60</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107190</t>
+          <t xml:space="preserve">9722879</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>1435</v>
+        <v>783</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892637</t>
+          <t xml:space="preserve">311892648</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 60</t>
+          <t xml:space="preserve">Krogen 3</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722879</t>
+          <t xml:space="preserve">100019865</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J182">
-        <v>783</v>
+        <v>799</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892648</t>
+          <t xml:space="preserve">311892885</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 3</t>
+          <t xml:space="preserve">Krogen 5</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13706,15 +13706,15 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892885</t>
+          <t xml:space="preserve">311892716</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 5</t>
+          <t xml:space="preserve">Krogen 7</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13781,15 +13781,15 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J184">
-        <v>827</v>
+        <v>114</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892716</t>
+          <t xml:space="preserve">311892886</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krogen 7</t>
+          <t xml:space="preserve">Pramstedvej 6</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,20 +13851,20 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019865</t>
+          <t xml:space="preserve">5755576</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J185">
-        <v>114</v>
+        <v>1289</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892886</t>
+          <t xml:space="preserve">311892803</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,30 +13916,30 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pramstedvej 6</t>
+          <t xml:space="preserve">Smedebakken 14</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755576</t>
+          <t xml:space="preserve">5130812</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J186">
-        <v>1289</v>
+        <v>672</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892803</t>
+          <t xml:space="preserve">311892655</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 14</t>
+          <t xml:space="preserve">Smedebakken 16</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14006,15 +14006,15 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>672</v>
+        <v>1285</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892655</t>
+          <t xml:space="preserve">311892656</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14081,11 +14081,11 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>1285</v>
+        <v>815</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -14156,15 +14156,15 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J189">
-        <v>815</v>
+        <v>402</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892656</t>
+          <t xml:space="preserve">311892652</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 16</t>
+          <t xml:space="preserve">Sønder Allé 18A</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130812</t>
+          <t xml:space="preserve">5098976</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>402</v>
+        <v>3082</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892652</t>
+          <t xml:space="preserve">311892807</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J191">
-        <v>3082</v>
+        <v>1082</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J192">
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J193">
-        <v>1082</v>
+        <v>343</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18A</t>
+          <t xml:space="preserve">Sønder Allé 18B</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,20 +14526,20 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098976</t>
+          <t xml:space="preserve">5098950</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>343</v>
+        <v>664</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892807</t>
+          <t xml:space="preserve">311892805</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14606,11 +14606,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J195">
-        <v>664</v>
+        <v>1460</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Allé 18B</t>
+          <t xml:space="preserve">Vestergade 27</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5098950</t>
+          <t xml:space="preserve">5087533</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J196">
-        <v>1460</v>
+        <v>293</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892805</t>
+          <t xml:space="preserve">311892646</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 27</t>
+          <t xml:space="preserve">Vestergade 31</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,15 +14756,15 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J197">
-        <v>293</v>
+        <v>450</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892646</t>
+          <t xml:space="preserve">311892645</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 31</t>
+          <t xml:space="preserve">Viaduktvej 25B</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087533</t>
+          <t xml:space="preserve">5083002</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>450</v>
+        <v>505</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892645</t>
+          <t xml:space="preserve">311892650</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viaduktvej 25B</t>
+          <t xml:space="preserve">Østervang 3A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6870</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5083002</t>
+          <t xml:space="preserve">8257259</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>505</v>
+        <v>1222</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892650</t>
+          <t xml:space="preserve">311892719</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østervang 3A</t>
+          <t xml:space="preserve">Lundvej 135A</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8257259</t>
+          <t xml:space="preserve">1511389</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>1222</v>
+        <v>3433</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892719</t>
+          <t xml:space="preserve">311895818</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-22</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15056,11 +15056,11 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J201">
-        <v>3433</v>
+        <v>1008</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -15131,11 +15131,11 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J202">
-        <v>1008</v>
+        <v>827</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135A</t>
+          <t xml:space="preserve">Lundvej 135B</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15206,15 +15206,15 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J203">
-        <v>827</v>
+        <v>365</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895818</t>
+          <t xml:space="preserve">311895828</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15281,15 +15281,15 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J204">
-        <v>365</v>
+        <v>859</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895828</t>
+          <t xml:space="preserve">311895826</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundvej 135B</t>
+          <t xml:space="preserve">Abildvej 25</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1511389</t>
+          <t xml:space="preserve">8443476</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J205">
-        <v>859</v>
+        <v>1632</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311895826</t>
+          <t xml:space="preserve">311896763</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-22</t>
+          <t xml:space="preserve">2036-04-24</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15431,11 +15431,11 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J206">
-        <v>1632</v>
+        <v>2198</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15491,30 +15491,30 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abildvej 25</t>
+          <t xml:space="preserve">Byagervej 19</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8443476</t>
+          <t xml:space="preserve">5099692</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>2198</v>
+        <v>4785</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896763</t>
+          <t xml:space="preserve">311896775</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byagervej 19</t>
+          <t xml:space="preserve">Carolineparken 1A</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5099692</t>
+          <t xml:space="preserve">5757501</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>4785</v>
+        <v>1634</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896775</t>
+          <t xml:space="preserve">311896772</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1A</t>
+          <t xml:space="preserve">Carolineparken 1G</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15656,11 +15656,11 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J209">
-        <v>1634</v>
+        <v>567</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15716,30 +15716,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolineparken 1G</t>
+          <t xml:space="preserve">Fåborgvej 151</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6753</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757501</t>
+          <t xml:space="preserve">5112648</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>567</v>
+        <v>2385</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896772</t>
+          <t xml:space="preserve">311896787</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15791,30 +15791,30 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fåborgvej 151</t>
+          <t xml:space="preserve">Kirkegade 1C</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6753</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5112648</t>
+          <t xml:space="preserve">5107106</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J211">
-        <v>2385</v>
+        <v>390</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896787</t>
+          <t xml:space="preserve">311896773</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,30 +15866,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 1C</t>
+          <t xml:space="preserve">Møllegården 2</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6855</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5107106</t>
+          <t xml:space="preserve">5106049</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>390</v>
+        <v>996</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896773</t>
+          <t xml:space="preserve">311896762</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J213">
-        <v>996</v>
+        <v>1078</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegården 2</t>
+          <t xml:space="preserve">Solhøjvej 1</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6855</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106049</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>1078</v>
+        <v>760</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896762</t>
+          <t xml:space="preserve">311896782</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,17 +16091,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solhøjvej 1</t>
+          <t xml:space="preserve">Strandvejen 9B</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">8939771</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>760</v>
+        <v>218</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896782</t>
+          <t xml:space="preserve">311896791</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,17 +16166,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 9B</t>
+          <t xml:space="preserve">Stålværksvej 13A</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8939771</t>
+          <t xml:space="preserve">5756440</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>218</v>
+        <v>2835</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896791</t>
+          <t xml:space="preserve">311896789</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stålværksvej 13A</t>
+          <t xml:space="preserve">Sønderskovvej 33A</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,20 +16251,20 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756440</t>
+          <t xml:space="preserve">7277566</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J217">
-        <v>2835</v>
+        <v>431</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896789</t>
+          <t xml:space="preserve">311896786</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 33A</t>
+          <t xml:space="preserve">Sønderskovvej 35A</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">7277566</t>
+          <t xml:space="preserve">5134840</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J218">
-        <v>431</v>
+        <v>724</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896786</t>
+          <t xml:space="preserve">311896785</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,30 +16391,30 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 35A</t>
+          <t xml:space="preserve">Torvegade 17</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5134840</t>
+          <t xml:space="preserve">8879067</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J219">
-        <v>724</v>
+        <v>537</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896785</t>
+          <t xml:space="preserve">311896774</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,30 +16466,30 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 17</t>
+          <t xml:space="preserve">Vinkelvej 16A</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">7200</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8879067</t>
+          <t xml:space="preserve">5130859</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J220">
-        <v>537</v>
+        <v>977</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896774</t>
+          <t xml:space="preserve">311896759</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 16A</t>
+          <t xml:space="preserve">Vinkelvej 2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J221">
-        <v>977</v>
+        <v>3842</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16616,17 +16616,17 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 2</t>
+          <t xml:space="preserve">Yderikvej 40</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">7200</t>
+          <t xml:space="preserve">6862</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5130859</t>
+          <t xml:space="preserve">100060726</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -16635,11 +16635,11 @@
         </is>
       </c>
       <c r="J222">
-        <v>3842</v>
+        <v>2426</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896759</t>
+          <t xml:space="preserve">311896788</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,17 +16691,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yderikvej 40</t>
+          <t xml:space="preserve">Østergade 17</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">6862</t>
+          <t xml:space="preserve">6823</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">100060726</t>
+          <t xml:space="preserve">5075750</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>2426</v>
+        <v>1157</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896788</t>
+          <t xml:space="preserve">311896790</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16781,11 +16781,11 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J224">
-        <v>1157</v>
+        <v>2462</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -16856,11 +16856,11 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J225">
-        <v>2462</v>
+        <v>1302</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -16931,11 +16931,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J226">
-        <v>1302</v>
+        <v>107</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J227">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 17</t>
+          <t xml:space="preserve">Fyrvej 106</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">6823</t>
+          <t xml:space="preserve">6857</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5075750</t>
+          <t xml:space="preserve">5101218</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>450</v>
+        <v>136</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896790</t>
+          <t xml:space="preserve">311896981</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-24</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,17 +17141,17 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrvej 106</t>
+          <t xml:space="preserve">Lyngparken 3</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">6857</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">5101218</t>
+          <t xml:space="preserve">5755189</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>136</v>
+        <v>1252</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896981</t>
+          <t xml:space="preserve">311896976</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,30 +17216,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngparken 3</t>
+          <t xml:space="preserve">Nybrovej 30</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6851</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">5755189</t>
+          <t xml:space="preserve">736957, 5094333</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J230">
-        <v>1252</v>
+        <v>351</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896976</t>
+          <t xml:space="preserve">311896971</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 30</t>
+          <t xml:space="preserve">Nybrovej 32</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17306,15 +17306,15 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J231">
-        <v>351</v>
+        <v>1533</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896971</t>
+          <t xml:space="preserve">311896972</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 32</t>
+          <t xml:space="preserve">Nybrovej 34</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,20 +17376,20 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">736957, 5094333</t>
+          <t xml:space="preserve">5094366</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J232">
-        <v>1533</v>
+        <v>441</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896972</t>
+          <t xml:space="preserve">311896973</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 34</t>
+          <t xml:space="preserve">Nybrovej 36A</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,15 +17456,15 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>441</v>
+        <v>2976</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896973</t>
+          <t xml:space="preserve">311896980</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17516,17 +17516,17 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 36A</t>
+          <t xml:space="preserve">Roustvej 111</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">6851</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5094366</t>
+          <t xml:space="preserve">5757779</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,11 +17535,11 @@
         </is>
       </c>
       <c r="J234">
-        <v>2976</v>
+        <v>197</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896980</t>
+          <t xml:space="preserve">311896968</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17591,17 +17591,17 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roustvej 111</t>
+          <t xml:space="preserve">Skolegade 59</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6830</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5757779</t>
+          <t xml:space="preserve">5096151</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -17610,11 +17610,11 @@
         </is>
       </c>
       <c r="J235">
-        <v>197</v>
+        <v>933</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896968</t>
+          <t xml:space="preserve">311896982</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>933</v>
+        <v>1485</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 59</t>
+          <t xml:space="preserve">Torvet 7</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6830</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5096151</t>
+          <t xml:space="preserve">5753906</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>1485</v>
+        <v>3584</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896982</t>
+          <t xml:space="preserve">311896977</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,17 +17816,17 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 7</t>
+          <t xml:space="preserve">Vænget 26A</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6818</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5753906</t>
+          <t xml:space="preserve">5106609</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -17835,16 +17835,16 @@
         </is>
       </c>
       <c r="J238">
-        <v>3584</v>
+        <v>1477</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896978</t>
+          <t xml:space="preserve">311896979</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -17891,17 +17891,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vænget 26A</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">6818</t>
+          <t xml:space="preserve">6840</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5106609</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -17910,11 +17910,11 @@
         </is>
       </c>
       <c r="J239">
-        <v>1477</v>
+        <v>650</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896979</t>
+          <t xml:space="preserve">311897259</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-04-28</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17981,15 +17981,15 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J240">
-        <v>650</v>
+        <v>713</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897259</t>
+          <t xml:space="preserve">311897257</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18056,11 +18056,11 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J241">
-        <v>713</v>
+        <v>240</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -18131,15 +18131,15 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J242">
-        <v>240</v>
+        <v>1368</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897257</t>
+          <t xml:space="preserve">311897256</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J243">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J244">
@@ -18356,15 +18356,15 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J245">
-        <v>1368</v>
+        <v>217</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897256</t>
+          <t xml:space="preserve">311897258</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Skolevænget 12A</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18431,15 +18431,15 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J246">
-        <v>217</v>
+        <v>437</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897258</t>
+          <t xml:space="preserve">311897264</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12A</t>
+          <t xml:space="preserve">Skolevænget 19</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,20 +18501,20 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">5087702</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J247">
-        <v>437</v>
+        <v>1155</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897264</t>
+          <t xml:space="preserve">311897265</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 19</t>
+          <t xml:space="preserve">Torps Alle 4</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087702</t>
+          <t xml:space="preserve">5088166</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -18585,11 +18585,11 @@
         </is>
       </c>
       <c r="J248">
-        <v>1155</v>
+        <v>695</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897265</t>
+          <t xml:space="preserve">311897266</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torps Alle 4</t>
+          <t xml:space="preserve">Skolevænget 12</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,20 +18651,20 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5088166</t>
+          <t xml:space="preserve">8839667</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J249">
-        <v>695</v>
+        <v>726</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897266</t>
+          <t xml:space="preserve">311897625</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-28</t>
+          <t xml:space="preserve">2036-04-29</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18731,11 +18731,11 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J250">
-        <v>726</v>
+        <v>5084</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -18776,12 +18776,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varde Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 12</t>
+          <t xml:space="preserve">Præstegaardsvej 19A</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,30 +18801,30 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">8839667</t>
+          <t xml:space="preserve">737156, 5088041</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">138</t>
         </is>
       </c>
       <c r="J251">
-        <v>5084</v>
+        <v>434</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311897625</t>
+          <t xml:space="preserve">311900035</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-29</t>
+          <t xml:space="preserve">2036-05-08</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Varde Kommune</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -18866,40 +18866,40 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegaardsvej 19A</t>
+          <t xml:space="preserve">Lerpøtvej 55</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840</t>
+          <t xml:space="preserve">6800</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">737156, 5088041</t>
+          <t xml:space="preserve">5756829</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">138</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J252">
-        <v>434</v>
+        <v>2680</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311900035</t>
+          <t xml:space="preserve">311918684</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-08</t>
+          <t xml:space="preserve">2036-08-12</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18956,15 +18956,15 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J253">
-        <v>2680</v>
+        <v>2277</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918684</t>
+          <t xml:space="preserve">311918683</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19031,15 +19031,15 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J254">
-        <v>2277</v>
+        <v>3746</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918683</t>
+          <t xml:space="preserve">311918682</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19106,11 +19106,11 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J255">
-        <v>3746</v>
+        <v>646</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55</t>
+          <t xml:space="preserve">Lerpøtvej 55A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -19181,11 +19181,11 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J256">
-        <v>646</v>
+        <v>956</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -19241,40 +19241,40 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerpøtvej 55A</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">6800</t>
+          <t xml:space="preserve">6870</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5756829</t>
+          <t xml:space="preserve">8290907</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>956</v>
+        <v>341</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918682</t>
+          <t xml:space="preserve">311931080</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Danske Bygningsrådgivere ApS</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-12</t>
+          <t xml:space="preserve">2036-10-09</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
